--- a/rp/Excel/Interact_交互物表.xlsx
+++ b/rp/Excel/Interact_交互物表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9015"/>
+    <workbookView windowWidth="24750" windowHeight="12060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="393">
   <si>
     <t>int</t>
   </si>
@@ -1152,6 +1152,60 @@
   </si>
   <si>
     <t>0A031A75</t>
+  </si>
+  <si>
+    <t>16A61F87</t>
+  </si>
+  <si>
+    <t>Tung</t>
+  </si>
+  <si>
+    <t>2D8ED710</t>
+  </si>
+  <si>
+    <t>NikeShark</t>
+  </si>
+  <si>
+    <t>2D3EB199</t>
+  </si>
+  <si>
+    <t>kapibalaCoco</t>
+  </si>
+  <si>
+    <t>32B156FF</t>
+  </si>
+  <si>
+    <t>CowPlanet</t>
+  </si>
+  <si>
+    <t>186AA55A</t>
+  </si>
+  <si>
+    <t>StagLord</t>
+  </si>
+  <si>
+    <t>1FF1A07C</t>
+  </si>
+  <si>
+    <t>CupNin</t>
+  </si>
+  <si>
+    <t>13CAB8F6</t>
+  </si>
+  <si>
+    <t>wheelfog</t>
+  </si>
+  <si>
+    <t>1CAAEA77</t>
+  </si>
+  <si>
+    <t>CamelRefrigerator</t>
+  </si>
+  <si>
+    <t>351DE976</t>
+  </si>
+  <si>
+    <t>BananaMonkey</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1218,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1185,6 +1239,19 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF303133"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1641,28 +1708,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1671,122 +1729,131 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1805,6 +1872,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2126,7 +2197,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q214"/>
+  <dimension ref="A1:Q231"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -8044,6 +8115,156 @@
       <c r="P214" s="1"/>
       <c r="Q214" s="1"/>
     </row>
+    <row r="215" spans="1:9">
+      <c r="A215" s="2">
+        <v>211</v>
+      </c>
+      <c r="B215" t="s">
+        <v>375</v>
+      </c>
+      <c r="E215">
+        <v>70001</v>
+      </c>
+      <c r="I215" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="216" ht="15.75" spans="1:9">
+      <c r="A216" s="2">
+        <v>212</v>
+      </c>
+      <c r="B216" t="s">
+        <v>377</v>
+      </c>
+      <c r="E216">
+        <v>70002</v>
+      </c>
+      <c r="I216" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="217" ht="15.75" spans="1:9">
+      <c r="A217" s="2">
+        <v>213</v>
+      </c>
+      <c r="B217" t="s">
+        <v>379</v>
+      </c>
+      <c r="E217">
+        <v>70003</v>
+      </c>
+      <c r="I217" s="7" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="218" ht="15.75" spans="1:9">
+      <c r="A218" s="2">
+        <v>214</v>
+      </c>
+      <c r="B218" t="s">
+        <v>381</v>
+      </c>
+      <c r="E218">
+        <v>70004</v>
+      </c>
+      <c r="I218" s="7" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="219" ht="15.75" spans="1:9">
+      <c r="A219" s="2">
+        <v>215</v>
+      </c>
+      <c r="B219" t="s">
+        <v>383</v>
+      </c>
+      <c r="E219">
+        <v>70005</v>
+      </c>
+      <c r="I219" s="7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="220" ht="15.75" spans="1:9">
+      <c r="A220" s="2">
+        <v>216</v>
+      </c>
+      <c r="B220" t="s">
+        <v>385</v>
+      </c>
+      <c r="E220">
+        <v>70006</v>
+      </c>
+      <c r="I220" s="7" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="221" ht="15.75" spans="1:9">
+      <c r="A221" s="2">
+        <v>217</v>
+      </c>
+      <c r="B221" t="s">
+        <v>387</v>
+      </c>
+      <c r="E221">
+        <v>70007</v>
+      </c>
+      <c r="I221" s="7" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="222" ht="15.75" spans="1:9">
+      <c r="A222" s="2">
+        <v>218</v>
+      </c>
+      <c r="B222" t="s">
+        <v>389</v>
+      </c>
+      <c r="E222">
+        <v>70008</v>
+      </c>
+      <c r="I222" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" s="2">
+        <v>219</v>
+      </c>
+      <c r="B223" t="s">
+        <v>391</v>
+      </c>
+      <c r="E223">
+        <v>70009</v>
+      </c>
+      <c r="I223" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="2"/>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="2"/>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="2"/>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="2"/>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="2"/>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="2"/>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="2"/>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
